--- a/static/standards-correlations/California_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/California_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$34</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | California CS Standards, September 2018</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | California CS Standards, September 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -879,7 +880,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Ext 1.1F (Why a PIN?) compares a short numeric PIN against a longer password as authentication. Discovery Systems 10 covers phishing. Extension-only.</t>
+          <t>Ext 1.1F (Why a PIN?) compares a short numeric PIN against a longer password as authentication. Introductory Systems 10 covers phishing. Extension-only.</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1561,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Unit 5.3 teaches version control, repositories, and commits directly. Discovery Systems 13 and 14 assign roles and manage a timeline.</t>
+          <t>Unit 5.3 teaches version control, repositories, and commits directly. Introductory Systems 13 and 14 assign roles and manage a timeline.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2002,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2045,7 +2047,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2059,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2171,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
@@ -2186,7 +2190,7 @@
 LINEAGE: California's standards are built on the K-12 Computer Science Framework and CSTA. Concept and subconcept names mirror that framework; identifiers are California's own.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 An earlier revision of this file scored lab FRONT MATTER ONLY (headings, descriptions, concept tags, objectives) and materially undercounted coverage. Those figures are superseded.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?' in the labs), or where the standard is only partly met. Cells citing 'Ext N.NL' identify the specific extension carrying the evidence, so a reviewer can verify placement and decide whether optional work counts for their purposes.</t>
         </is>
